--- a/sheets/민요/검수/박연폭포 (굿거리).xlsx
+++ b/sheets/민요/검수/박연폭포 (굿거리).xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -589,12 +589,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I3" s="2"/>
@@ -624,19 +624,19 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―</t>
+          <t xml:space="preserve">–|–</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">짧은 선 둘 + 점(―/―/·), 3개 규칙대로 나눔</t>
+          <t xml:space="preserve">짧은 선 둘 + 점(–/–/·), 3개 규칙대로 나눔</t>
         </is>
       </c>
       <c r="K4" s="2"/>
@@ -699,13 +699,13 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―汰</t>
+          <t xml:space="preserve">潢|–汰</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="2"/>
@@ -924,13 +924,13 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|―南</t>
+          <t xml:space="preserve">無|–南</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1003,13 +1003,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―㳞</t>
+          <t xml:space="preserve">潢|–㳞</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1118,13 +1118,13 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|―△</t>
+          <t xml:space="preserve">–|–△</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―△</t>
+          <t xml:space="preserve">–
+–△</t>
         </is>
       </c>
       <c r="I17" s="2"/>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I21" s="2"/>
@@ -1344,12 +1344,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I23" s="2"/>
@@ -1458,13 +1458,13 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
@@ -1616,13 +1616,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―無</t>
+          <t xml:space="preserve">汰|–無</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="I30" s="2"/>
@@ -1691,13 +1691,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -1807,7 +1807,7 @@
       <c r="C4" s="9"/>
       <c r="D4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="9"/>
@@ -1827,8 +1827,8 @@
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―</t>
+          <t xml:space="preserve">–
+–</t>
         </is>
       </c>
       <c r="E5" s="12"/>
@@ -1837,7 +1837,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C6" s="10"/>
@@ -1864,7 +1864,7 @@
       <c r="D7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -1877,7 +1877,7 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="9"/>
@@ -1933,7 +1933,7 @@
       <c r="B11" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1963,7 +1963,7 @@
       <c r="C12" s="9"/>
       <c r="D12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E12" s="9"/>
@@ -1984,7 +1984,7 @@
       <c r="D13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="E13" s="9" t="inlineStr">
@@ -2021,14 +2021,14 @@
       <c r="B15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―無</t>
+–無</t>
         </is>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -2061,7 +2061,7 @@
       <c r="B17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
@@ -2091,8 +2091,8 @@
       <c r="C18" s="10"/>
       <c r="D18" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
-―△</t>
+          <t xml:space="preserve">–
+–△</t>
         </is>
       </c>
       <c r="E18" s="10"/>

--- a/sheets/민요/검수/박연폭포 (굿거리).xlsx
+++ b/sheets/민요/검수/박연폭포 (굿거리).xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1763,35 +1804,35 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">박연폭포</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">범</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">박연</t>
         </is>
@@ -1799,75 +1840,75 @@
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="23"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
+      <c r="E4" s="23"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南仲
 姑</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="D5" s="18" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –</t>
         </is>
       </c>
-      <c r="E5" s="12"/>
+      <c r="E5" s="25"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="26"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E6" s="10"/>
+      <c r="E6" s="26"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 南</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">정으</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –汰</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="E7" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">폭</t>
         </is>
@@ -1875,39 +1916,39 @@
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="23"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="23"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無南</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">포</t>
         </is>
@@ -1915,39 +1956,39 @@
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
+      <c r="E10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">감</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">흘러</t>
         </is>
@@ -1955,39 +1996,39 @@
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="23"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
+      <c r="E12" s="23"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞潢</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">돌</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 –南</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">내리</t>
         </is>
@@ -1995,22 +2036,22 @@
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C14" s="10" t="inlineStr">
+      <c r="C14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -2018,20 +2059,20 @@
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –無</t>
         </is>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –㳞</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">물</t>
         </is>
@@ -2039,43 +2080,43 @@
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
+      <c r="E16" s="23"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 南</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -2083,19 +2124,19 @@
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="26"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –△</t>
         </is>
       </c>
-      <c r="E18" s="10"/>
+      <c r="E18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/박연폭포 (굿거리).xlsx
+++ b/sheets/민요/검수/박연폭포 (굿거리).xlsx
@@ -1793,16 +1793,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="E4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="E5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -1884,12 +1884,12 @@
       <c r="C6" s="26"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E6" s="26"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -1914,7 +1914,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="E8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="24" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
       </c>
       <c r="E10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="24" t="inlineStr">
         <is>
@@ -1994,11 +1994,11 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="23"/>
@@ -2009,7 +2009,7 @@
       </c>
       <c r="E12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -2078,7 +2078,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/박연폭포 (굿거리).xlsx
+++ b/sheets/민요/검수/박연폭포 (굿거리).xlsx
@@ -1834,7 +1834,8 @@
       </c>
       <c r="E3" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">박연</t>
+          <t xml:space="preserve">박
+연</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1900,8 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">정으</t>
+          <t xml:space="preserve">정
+으</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -1990,7 +1992,8 @@
       </c>
       <c r="E11" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">흘러</t>
+          <t xml:space="preserve">흘
+러</t>
         </is>
       </c>
     </row>
@@ -2030,7 +2033,8 @@
       </c>
       <c r="E13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">내리</t>
+          <t xml:space="preserve">내
+리</t>
         </is>
       </c>
     </row>

--- a/sheets/민요/검수/박연폭포 (굿거리).xlsx
+++ b/sheets/민요/검수/박연폭포 (굿거리).xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,6 +239,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1821,7 +1844,7 @@
 南</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">범</t>
         </is>
@@ -1832,7 +1855,7 @@
 潢</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">박
 연</t>
@@ -1846,13 +1869,13 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C4" s="23"/>
+      <c r="C4" s="30"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="23"/>
+      <c r="E4" s="30"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -1862,7 +1885,7 @@
 姑</t>
         </is>
       </c>
-      <c r="C5" s="23" t="inlineStr">
+      <c r="C5" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -1873,7 +1896,7 @@
 –</t>
         </is>
       </c>
-      <c r="E5" s="25"/>
+      <c r="E5" s="31"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -1882,13 +1905,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="26"/>
+      <c r="C6" s="32"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E6" s="26"/>
+      <c r="E6" s="32"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -1898,7 +1921,7 @@
 南</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">정
 으</t>
@@ -1910,7 +1933,7 @@
 –汰</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">폭</t>
         </is>
@@ -1923,13 +1946,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="23"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E8" s="23"/>
+      <c r="E8" s="30"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -1939,7 +1962,7 @@
 無南</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">로</t>
         </is>
@@ -1950,7 +1973,7 @@
 汰</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">포</t>
         </is>
@@ -1963,13 +1986,13 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E10" s="26"/>
+      <c r="E10" s="32"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -1979,7 +2002,7 @@
 –</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">감</t>
         </is>
@@ -1990,7 +2013,7 @@
 南</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">흘
 러</t>
@@ -2004,13 +2027,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="23"/>
+      <c r="C12" s="30"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="23"/>
+      <c r="E12" s="30"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
@@ -2020,7 +2043,7 @@
 㳞潢</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">돌</t>
         </is>
@@ -2031,7 +2054,7 @@
 –南</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">내
 리</t>
@@ -2045,7 +2068,7 @@
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="C14" s="26" t="inlineStr">
+      <c r="C14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -2055,7 +2078,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E14" s="26" t="inlineStr">
+      <c r="E14" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
@@ -2069,14 +2092,14 @@
 –無</t>
         </is>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="29"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –㳞</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">물</t>
         </is>
@@ -2089,7 +2112,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">든</t>
         </is>
@@ -2099,7 +2122,7 @@
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E16" s="23"/>
+      <c r="E16" s="30"/>
     </row>
     <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
@@ -2109,7 +2132,7 @@
 –</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
@@ -2120,7 +2143,7 @@
 南</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">은</t>
         </is>
@@ -2133,14 +2156,14 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C18" s="26"/>
+      <c r="C18" s="32"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 –△</t>
         </is>
       </c>
-      <c r="E18" s="26"/>
+      <c r="E18" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/박연폭포 (굿거리).xlsx
+++ b/sheets/민요/검수/박연폭포 (굿거리).xlsx
@@ -737,10 +737,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/박연폭포 (굿거리).xlsx
+++ b/sheets/민요/검수/박연폭포 (굿거리).xlsx
@@ -413,25 +413,9 @@
     <t xml:space="preserve">아</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㴌
+    <t xml:space="preserve">㴌
 –
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+–</t>
   </si>
   <si>
     <t xml:space="preserve">㴌
@@ -451,84 +435,18 @@
 여</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–汰
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">정
-으</t>
-  </si>
-  <si>
     <t xml:space="preserve">㴌
 –汰
 㴌</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">汰</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">南
-無南</t>
+    <t xml:space="preserve">정
+으</t>
+  </si>
+  <si>
+    <t xml:space="preserve">㴌
+–汰
+㴌</t>
   </si>
   <si>
     <t xml:space="preserve">㴌
@@ -536,24 +454,17 @@
 㴌汰</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–</t>
-    </r>
+    <t xml:space="preserve">南
+無南</t>
+  </si>
+  <si>
+    <t xml:space="preserve">㴌
+汰
+㴌汰</t>
+  </si>
+  <si>
+    <t xml:space="preserve">㴌
+–</t>
   </si>
   <si>
     <t xml:space="preserve">無
@@ -575,63 +486,14 @@
 러</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">㳞</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">㴌
+    <t xml:space="preserve">㴌
+㳞㴌
+無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">無
+㴌
 㴌</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">좋
@@ -678,17 +540,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -810,7 +672,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -872,6 +734,54 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2330,236 +2240,236 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="52.63" customHeight="true">
+      <c r="B2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B3" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="20" t="s">
         <v>98</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="20" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B4" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="C4" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="7" t="s">
+      <c r="E4" s="21"/>
+      <c r="F4" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="I4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+      <c r="I4" s="21"/>
+    </row>
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B5" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C5" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="22" t="s">
         <v>121</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="E5" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="I5" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B6" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="E6" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="24" t="s">
         <v>125</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="I6" s="11" t="s">
+      <c r="I6" s="23" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="14" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B7" s="26" t="s">
         <v>127</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="27" t="s">
         <v>85</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="20" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="10" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B8" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="F8" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="21" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B9" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="F9" s="7" t="s">
+      <c r="F9" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="21" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="102.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="117.4" customHeight="true">
+      <c r="B10" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="23" t="s">
         <v>115</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="E10" s="11" t="s">
+      <c r="E10" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="G10" s="11" t="s">
+      <c r="G10" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="I10" s="11" t="s">
+      <c r="I10" s="23" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2569,7 +2479,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="76"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/박연폭포 (굿거리).xlsx
+++ b/sheets/민요/검수/박연폭포 (굿거리).xlsx
@@ -2246,13 +2246,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="6"/>
   </cols>
   <sheetData>
